--- a/files/l3/l3_otchet_ot_ii.xlsx
+++ b/files/l3/l3_otchet_ot_ii.xlsx
@@ -455,17 +455,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Номер месяца</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Месяц</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Сумма</t>
+          <t>Суммарная выручка</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <f>SUMIF(D$2:D$7,E2,C$2:C$7)</f>
+        <f>SUMIF(D:D,E2,C:C)</f>
         <v/>
       </c>
     </row>
@@ -510,10 +510,10 @@
         <v/>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <f>SUMIF(D$2:D$7,E3,C$2:C$7)</f>
+        <f>SUMIF(D:D,E3,C:C)</f>
         <v/>
       </c>
     </row>
@@ -534,10 +534,10 @@
         <v/>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <f>SUMIF(D$2:D$7,E4,C$2:C$7)</f>
+        <f>SUMIF(D:D,E4,C:C)</f>
         <v/>
       </c>
     </row>
@@ -557,13 +557,6 @@
         <f>MONTH(A5)</f>
         <v/>
       </c>
-      <c r="E5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <f>SUMIF(D$2:D$7,E5,C$2:C$7)</f>
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -581,13 +574,6 @@
         <f>MONTH(A6)</f>
         <v/>
       </c>
-      <c r="E6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <f>SUMIF(D$2:D$7,E6,C$2:C$7)</f>
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -603,13 +589,6 @@
       </c>
       <c r="D7">
         <f>MONTH(A7)</f>
-        <v/>
-      </c>
-      <c r="E7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7">
-        <f>SUMIF(D$2:D$7,E7,C$2:C$7)</f>
         <v/>
       </c>
     </row>
